--- a/AAII_Financials/Yearly/ORCL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ORCL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>ORCL</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>45808</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45443</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44712</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44347</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43982</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43616</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43251</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42886</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42521</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42155</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41790</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41425</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41060</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>67357000</v>
+      </c>
+      <c r="E8" s="3">
         <v>57399000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>52961000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>49954000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42440000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>40479000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>39068000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>39506000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39383000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>37792000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37047000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38226000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38275000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37180000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37121000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>23021000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16927000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15143000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13564000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8877000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7855000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7938000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7995000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8060000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10444000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7479000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7526000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7236000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7379000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7858000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>44336000</v>
+      </c>
+      <c r="E10" s="3">
         <v>40472000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37818000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>36390000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>33563000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32624000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31130000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31511000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31323000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27348000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>29568000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30700000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>31039000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29801000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29263000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>10272000</v>
+      </c>
+      <c r="E12" s="3">
         <v>9860000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8915000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8623000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7219000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6527000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6067000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6026000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6084000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6153000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5787000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5524000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5151000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4850000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4523000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -983,105 +999,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>554000</v>
+        <v>-1032000</v>
       </c>
       <c r="E14" s="3">
-        <v>714000</v>
+        <v>577000</v>
       </c>
       <c r="F14" s="3">
+        <v>707000</v>
+      </c>
+      <c r="G14" s="3">
         <v>904000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5057000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>178000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>255000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>471000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>637000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>566000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>500000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>418000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>224000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-252000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>351000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1671000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2307000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3010000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3582000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1150000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1379000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1586000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1689000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1620000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2902000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1638000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2149000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2300000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2385000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2430000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>39445000</v>
+        <v>44972000</v>
       </c>
       <c r="E17" s="3">
-        <v>37197000</v>
+        <v>39422000</v>
       </c>
       <c r="F17" s="3">
+        <v>37204000</v>
+      </c>
+      <c r="G17" s="3">
         <v>36284000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26604000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24826000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24917000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25500000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25482000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24879000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24443000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24355000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23516000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22496000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23415000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>17954000</v>
+        <v>22385000</v>
       </c>
       <c r="E18" s="3">
-        <v>15764000</v>
+        <v>17977000</v>
       </c>
       <c r="F18" s="3">
+        <v>15757000</v>
+      </c>
+      <c r="G18" s="3">
         <v>13670000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15836000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15653000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14151000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14006000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13901000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12913000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12604000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13871000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14759000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14684000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13706000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1213,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E20" s="3">
         <v>240000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>246000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>420000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>469000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>81000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>365000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>277000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>565000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>305000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>106000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-141000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>11000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>20021000</v>
+        <v>24012000</v>
       </c>
       <c r="E21" s="3">
-        <v>18528000</v>
+        <v>20044000</v>
       </c>
       <c r="F21" s="3">
+        <v>18521000</v>
+      </c>
+      <c r="G21" s="3">
         <v>16832000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16517000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>16951000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15372000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15418000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15503000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15929000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15418000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16838000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17526000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17626000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16644000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>4599000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3578000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3514000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3505000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2755000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2496000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1995000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2082000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2025000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1798000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1467000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1143000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>914000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>797000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>766000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>19554000</v>
+      </c>
+      <c r="E23" s="3">
         <v>14160000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11741000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9126000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7649000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12999000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12063000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12268000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12424000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11680000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11442000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12834000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13704000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13898000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12962000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2467000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1717000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1274000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>623000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>932000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-747000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1928000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1185000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8837000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2228000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2541000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2896000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2749000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2973000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2981000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>17087000</v>
+      </c>
+      <c r="E26" s="3">
         <v>12443000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10467000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8503000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6717000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13746000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10135000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11083000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3587000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9452000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8901000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9938000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10955000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10925000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9981000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>16984000</v>
+      </c>
+      <c r="E27" s="3">
         <v>12443000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10467000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8503000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6717000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13746000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10135000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11083000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3587000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9452000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8901000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9938000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10955000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10925000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9981000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-240000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-246000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-420000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-469000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-81000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-365000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-277000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-565000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-305000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-106000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>141000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17087000</v>
+      </c>
+      <c r="E33" s="3">
         <v>12443000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10467000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8503000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6717000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13746000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10135000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11083000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3587000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9452000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8901000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9938000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10955000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10925000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9981000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17087000</v>
+      </c>
+      <c r="E35" s="3">
         <v>12443000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10467000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8503000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6717000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13746000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10135000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11083000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3587000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9452000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8901000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9938000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10955000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10925000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9981000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>45808</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45443</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44712</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44347</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43982</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43616</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43251</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42886</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42521</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42155</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41790</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41425</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41060</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,200 +2159,213 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31289000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10786000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10454000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9765000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21383000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>30098000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37239000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20514000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21620000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21784000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20152000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>21716000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17769000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14613000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14955000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>605000</v>
+      </c>
+      <c r="E42" s="3">
         <v>417000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>207000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>422000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>519000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>16456000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5818000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17313000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>45641000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44294000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>35973000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>32652000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21050000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17603000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>15721000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9413000</v>
+        <v>10385000</v>
       </c>
       <c r="E43" s="3">
+        <v>8558000</v>
+      </c>
+      <c r="F43" s="3">
         <v>8695000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7713000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6744000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6207000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6329000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5910000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5938000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5300000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5385000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5618000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6087000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6049000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6377000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>303000</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="3">
         <v>334000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>298000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>314000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>142000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>211000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>320000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>398000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>300000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>212000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>314000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>189000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>240000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>158000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2295,105 +2393,111 @@
       <c r="K45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="3">
         <v>2837000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2591000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2883000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3033000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3187000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2812000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46567000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24579000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22554000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21004000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>31633000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55567000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>52140000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46386000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76159000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>74515000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>64313000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>63183000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>48128000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>41692000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>40023000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2100000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2000000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1600000</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3">
         <v>29000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2409,105 +2513,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>129647000</v>
+      </c>
+      <c r="E48" s="3">
         <v>56667000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28826000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17069000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9716000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7049000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6244000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6252000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5897000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5315000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4000000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3686000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3061000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3053000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3021000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>65490000</v>
+      </c>
+      <c r="E49" s="3">
         <v>66794000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>69120000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>72098000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>45251000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46365000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>47507000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>49058000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>50425000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>50724000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>39533000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>40493000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>35789000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>33983000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21541000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6214000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6344000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6203000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10387000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9915000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8490000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6266000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4312000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3946000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4437000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4334000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3541000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3296000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3084000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3935000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>261759000</v>
+      </c>
+      <c r="E54" s="3">
         <v>168361000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>140976000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>134384000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>109297000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>131107000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>115438000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>108709000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>137851000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>134991000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>112180000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>110903000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>90266000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>81812000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78327000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10977000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5113000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2357000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1204000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1317000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>745000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>637000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>580000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>529000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>599000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>504000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>806000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>471000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>419000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>438000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11361000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9442000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11895000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4061000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3749000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8250000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2622000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4499000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4498000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9797000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3750000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1999000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1508000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>2950000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17201000</v>
+      </c>
+      <c r="E59" s="3">
         <v>15845000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15376000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15772000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12501000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13152000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12488000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11923000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12291000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13782000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12954000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12486000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12410000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12453000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12000000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41764000</v>
+      </c>
+      <c r="E60" s="3">
         <v>32643000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31544000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23090000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19511000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24164000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18630000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19124000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24178000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17208000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15291000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14389000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12872000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15388000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>156071000</v>
+      </c>
+      <c r="E61" s="3">
         <v>99510000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>82519000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>86420000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>72110000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>75995000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69243000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51898000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>56279000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47132000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39114000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>38978000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21473000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18494000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13524000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15389000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13893000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16441000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16578000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16660000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16453000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15640000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14885000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14892000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9435000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8068000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7536000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6957000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5301000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6601000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>218703000</v>
+      </c>
+      <c r="E66" s="3">
         <v>147392000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>131737000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>132828000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>115065000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>125155000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>102721000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>86346000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>90978000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>81131000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>64891000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>62240000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43388000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37164000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34639000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,14 +3545,17 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>4954000</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4309000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15481000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-22628000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-27620000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-31336000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-20120000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12696000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3496000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19111000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27598000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23888000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26503000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>25965000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25854000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26087000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>37554000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20451000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8704000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1073000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-6220000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5238000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12074000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21785000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46372000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>53860000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47289000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48663000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46878000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44648000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43688000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>45808</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45443</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44712</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44347</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43982</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43616</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43251</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42886</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42521</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42155</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41790</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41425</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41060</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17087000</v>
+      </c>
+      <c r="E81" s="3">
         <v>12443000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10467000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8503000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6717000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13746000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10135000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11083000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3587000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9452000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8901000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9938000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10955000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10925000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9981000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7623000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3867000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3129000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2526000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1972000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1537000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1382000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1230000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1165000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2451000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2509000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2861000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2908000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2931000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2916000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31977000</v>
+      </c>
+      <c r="E89" s="3">
         <v>20821000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18673000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17165000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9539000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15887000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13139000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14551000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15386000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14126000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13685000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14580000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14921000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14224000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13743000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-55663000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21215000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6866000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8695000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4511000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2135000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1564000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1660000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1736000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2021000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1189000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1391000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-580000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-650000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-648000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-51854000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21711000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7360000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-36484000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>11220000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13098000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>9843000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>26557000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5625000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21494000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5154000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19047000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7539000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5956000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8381000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5724000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4743000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4391000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3668000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3457000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3063000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3070000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2932000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3140000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2631000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2541000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2255000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2178000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1433000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1205000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>40284000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1098000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10554000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7910000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-29126000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10378000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6132000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-42056000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9982000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9086000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9980000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9606000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4068000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8500000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6099000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E101" s="3">
         <v>124000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-70000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-209000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-348000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>448000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-125000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-158000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>57000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-86000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-115000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1192000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-158000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-110000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-471000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20503000</v>
+      </c>
+      <c r="E102" s="3">
         <v>332000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>689000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11618000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8715000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7141000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16725000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1106000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-164000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1632000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1564000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3947000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3156000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-342000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1208000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
